--- a/data/mapas/Mapa_de_Carrera_Ciencias_Juridicas.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencias_Juridicas.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B34, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C34, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F34, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Introducción al Derecho y Teoría General</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B34, "SI")/24</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Derecho Político y Teoría del Estado</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C34, "SI")/24</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Historia de las Ideas e Instituciones Políticas</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Sociología Jurídica</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Derecho Constitucional y Garantías</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Derechos Humanos y Derecho Internacional de los DD.HH.</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Derecho Privado I (Parte General y Personas)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Derecho Penal I (Parte General)</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sujetos de la Educación</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1187,44 +1241,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Derecho Privado II (Obligaciones y Contratos)</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1266,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1258,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Derecho Administrativo</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Derecho del Trabajo y Relaciones Laborales</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Didáctica de las Ciencias Jurídicas I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Elementos de Derecho Procesal</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1435,14 +1489,14 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
+          <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior II</t>
+          <t>Derecho Internacional Público y de la Integración</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1457,7 +1511,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1476,7 +1530,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Finanzas Públicas y Derecho Tributario</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Derecho Ambiental y de los Recursos Naturales</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Didáctica de las Ciencias Jurídicas II</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,27 +1629,237 @@
         <v/>
       </c>
     </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Ética y Trabajo Docente</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E37" s="10">
+        <f>IF(B37="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>IF(C37="SI", "APROBADO", IF(B37="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
+        <f>IF(C37="SI", "🟢 Aprobada", IF(B37="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Derecho Constitucional Profundizado</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Género y Sistema de Justicia</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E40" s="10">
+        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Taller de Práctica Forense y Litigación Educativa</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E41" s="10">
+        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
+        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Ciencias_Juridicas.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencias_Juridicas.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B50, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C50, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F50, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Introducción al Derecho y Teoría General</t>
+          <t>Derecho político</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B50, "SI")/41</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Derecho Político y Teoría del Estado</t>
+          <t>Historia de las instituciones Argentinas 1</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C50, "SI")/41</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Historia de las Ideas e Instituciones Políticas</t>
+          <t>Historia de las ideas e instituciones politicas</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Sociología Jurídica</t>
+          <t>Historia de los hechos y de las ideas económicas</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Introducción al derecho</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Taller de expresión oral y escrita 1</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Pedagogia general</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Sociología general</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Derecho Constitucional y Garantías</t>
+          <t>Psicologia del desarrollo y del aprendizaje</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -1001,7 +1028,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos y Derecho Internacional de los DD.HH.</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1016,7 +1043,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1037,44 +1064,17 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Derecho Privado I (Parte General y Personas)</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E16" s="10">
-        <f>IF(B16="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF(C16="SI", "APROBADO", IF(B16="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IF(C16="SI", "🟢 Aprobada", IF(B16="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Derecho Penal I (Parte General)</t>
+          <t>Derecho privado 1</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Historia de las instituciones Argentinas 2</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Derecho penal y criminalidad</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Economía política</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Derecho constitucional</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Derechos humanos y garantias</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Derecho Privado II (Obligaciones y Contratos)</t>
+          <t>Didactica General</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1266,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1285,7 +1312,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Derecho Administrativo</t>
+          <t>Introducción a la filosofía</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1319,7 +1346,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Derecho del Trabajo y Relaciones Laborales</t>
+          <t>Taller de expresión oral y escrita 2</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de las Ciencias Jurídicas I</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1384,44 +1411,17 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Elementos de Derecho Procesal</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E27" s="10">
-        <f>IF(B27="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>IF(C27="SI", "APROBADO", IF(B27="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G27" s="11">
-        <f>IF(C27="SI", "🟢 Aprobada", IF(B27="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Derecho privado 2</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Derecho administrativo y municipal</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1486,17 +1486,44 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Elementos de derecho procesal y régimen legal de concursos y quiebras</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Derecho Internacional Público y de la Integración</t>
+          <t>Relaciones laborales y seguridad social</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1530,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Finanzas Públicas y Derecho Tributario</t>
+          <t>Demografía, ecología y geografía humana</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Derecho Ambiental y de los Recursos Naturales</t>
+          <t>Didactica especifica 1 y trabajo de campo 3</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de las Ciencias Jurídicas II</t>
+          <t>Estado, sociedad y DDHH</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Historia mundial contemporanea</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1663,44 +1690,17 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E36" s="10">
-        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
-        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G36" s="11">
-        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Derecho internacional público</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1731,51 +1731,51 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Derecho ambiental y de los recursos naturales</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E38" s="10">
+        <f>IF(B38="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IF(C38="SI", "APROBADO", IF(B38="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="11">
+        <f>IF(C38="SI", "🟢 Aprobada", IF(B38="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
         </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Derecho Constitucional Profundizado</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Tramo Superior / Seminarios</t>
-        </is>
-      </c>
-      <c r="E39" s="10">
-        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
-        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Género y Sistema de Justicia</t>
+          <t>Psicología social y jurídica</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1809,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taller de Práctica Forense y Litigación Educativa</t>
+          <t>Derecho de las comunicaciones de los transportes</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1840,26 +1840,332 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Nociones de etica</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Historia social de la educación</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica específica 2 y residencia</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Política educacional y legislación escolar</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Finanzas y legislación impositiva</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Taller optativo: El adulto como sujeto del aprendizaje</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Esi</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Politica educacional y legislación escolar</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Para cursar Trabajo de campo 1 es necesario estar cursando o haber cursado: • Pedagogía general • Psicología del desarrollo y del aprendizaje</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B28 B29 B30 B31 B32 B33 B34 B35 B37 B38 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C28 C29 C30 C31 C32 C33 C34 C35 C37 C38 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
